--- a/Result/profitability/2530.xlsx
+++ b/Result/profitability/2530.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>-0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3625</v>
+        <v>0.275</v>
       </c>
       <c r="N2" t="n">
-        <v>35.08875</v>
+        <v>27.04</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2762500000000001</v>
+        <v>0.21</v>
       </c>
       <c r="N3" t="n">
-        <v>34.3425</v>
+        <v>26.4225</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.20875</v>
+        <v>0.1975</v>
       </c>
       <c r="N4" t="n">
-        <v>34.94625</v>
+        <v>27.20625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.51</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01750000000000004</v>
+        <v>-0.145</v>
       </c>
       <c r="N5" t="n">
-        <v>1.822500000000002</v>
+        <v>-6.587499999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.125</v>
+        <v>-0.235</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5287500000000014</v>
+        <v>-7.279999999999998</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.68</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1412499999999999</v>
+        <v>-0.145</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.07999999999999829</v>
+        <v>-7.098749999999998</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.105</v>
+        <v>-0.10875</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7875000000000023</v>
+        <v>-4.672499999999998</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2530</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>22</v>
+      </c>
+      <c r="D75" t="n">
+        <v>27</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-38</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-170.51%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-61</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-59</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3750000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.40625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.03000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7500000000000002</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-43.68</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-2.219512195121951</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.056910569105691</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-67.28</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.55452865064695</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
